--- a/artfynd/A 60898-2025 artfynd.xlsx
+++ b/artfynd/A 60898-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1329269</v>
+        <v>1351896</v>
       </c>
       <c r="B2" t="n">
-        <v>90318</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>3674</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>653695.3880860537</v>
+        <v>653683</v>
       </c>
       <c r="R2" t="n">
-        <v>6678102.298319719</v>
+        <v>6678137</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,24 +752,14 @@
           <t>2006-10-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2006-10-07</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>16 ex.</t>
+          <t>1 ex.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,7 +773,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,15 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1351898</v>
+        <v>1351897</v>
       </c>
       <c r="B3" t="n">
-        <v>85240</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -843,7 +823,11 @@
           <t>Britzelm.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -855,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>653651.2424640444</v>
+        <v>653615</v>
       </c>
       <c r="R3" t="n">
-        <v>6678192.004582269</v>
+        <v>6678173</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,24 +872,14 @@
           <t>2006-10-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2006-10-07</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Spridda ex.</t>
+          <t>10 ex.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -941,15 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1351896</v>
+        <v>1351898</v>
       </c>
       <c r="B4" t="n">
-        <v>85240</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,11 +943,7 @@
           <t>Britzelm.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -990,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>653682.9586179297</v>
+        <v>653651</v>
       </c>
       <c r="R4" t="n">
-        <v>6678137.107062403</v>
+        <v>6678192</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,24 +988,14 @@
           <t>2006-10-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2006-10-07</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>1 ex.</t>
+          <t>Spridda ex.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1076,15 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1351897</v>
+        <v>1329269</v>
       </c>
       <c r="B5" t="n">
-        <v>85240</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,26 +1042,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3674</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1125,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>653614.6767716061</v>
+        <v>653695</v>
       </c>
       <c r="R5" t="n">
-        <v>6678172.553571122</v>
+        <v>6678102</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1158,24 +1108,14 @@
           <t>2006-10-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2006-10-07</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>10 ex.</t>
+          <t>16 ex.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1189,7 +1129,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1214,12 +1154,7 @@
         <v>1329270</v>
       </c>
       <c r="B6" t="n">
-        <v>90318</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1176,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1260,10 +1195,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>653690.4983366635</v>
+        <v>653690</v>
       </c>
       <c r="R6" t="n">
-        <v>6678159.319369255</v>
+        <v>6678159</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1293,19 +1228,9 @@
           <t>2006-10-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2006-10-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1339,6 +1264,122 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>Uppföljning av skyddade områden</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2429047</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Åsarby, Uddtäppan, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>653534</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6678214</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2006-05-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2006-05-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Riklig i örtrik översilning</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Uppföljning av skyddade områden</t>
         </is>

--- a/artfynd/A 60898-2025 artfynd.xlsx
+++ b/artfynd/A 60898-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2429047</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1351896</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1351897</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1144,6 +1164,11 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1351898</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1264,6 +1289,11 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1329269</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1384,8 +1414,21 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1329270</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>